--- a/Docs/RepartimentDesglo�Compra.xlsx
+++ b/Docs/RepartimentDesglo�Compra.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="80" windowWidth="19140" windowHeight="7340" activeTab="5"/>
+    <workbookView xWindow="80" yWindow="80" windowWidth="19140" windowHeight="7340" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="378">
   <si>
     <t>c1</t>
   </si>
@@ -1132,6 +1133,27 @@
   </si>
   <si>
     <t>orig</t>
+  </si>
+  <si>
+    <t>6-Biotechnology C USD Acc</t>
+  </si>
+  <si>
+    <t>European Growth N Acc ?</t>
+  </si>
+  <si>
+    <t>Asian Smaller Companies Fund</t>
+  </si>
+  <si>
+    <t>Biotechnology C USD Acc</t>
+  </si>
+  <si>
+    <t>Parts V</t>
+  </si>
+  <si>
+    <t>Parts V Orig</t>
+  </si>
+  <si>
+    <t>2-European Growth N Acc ?</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1166,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1181,8 +1203,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1204,8 +1240,19 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1222,14 +1269,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1283,8 +1347,18 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="5"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
+    <cellStyle name="20% - Accent4" xfId="5" builtinId="42"/>
+    <cellStyle name="Accent2" xfId="4" builtinId="33"/>
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -15055,4 +15129,482 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="9.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="6" max="7" width="9.6328125" hidden="1" customWidth="1"/>
+    <col min="8" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="30.81640625" customWidth="1"/>
+    <col min="13" max="13" width="2.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="D1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="10">
+        <v>7</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="11">
+        <v>41492</v>
+      </c>
+      <c r="D3" s="10">
+        <v>24.091999999999999</v>
+      </c>
+      <c r="E3" s="29">
+        <v>250.44120000000001</v>
+      </c>
+      <c r="F3" s="29">
+        <v>6033.63</v>
+      </c>
+      <c r="G3" s="29">
+        <v>6033.63</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="N3">
+        <f>D3</f>
+        <v>24.091999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="10">
+        <v>39</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="11">
+        <v>41673</v>
+      </c>
+      <c r="D4" s="31">
+        <v>3.1440000000000001</v>
+      </c>
+      <c r="E4" s="29">
+        <v>304.8664</v>
+      </c>
+      <c r="F4" s="29">
+        <v>958.5</v>
+      </c>
+      <c r="G4" s="29">
+        <v>958.5</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="N4">
+        <f>N3+D4</f>
+        <v>27.235999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="10">
+        <v>40</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="11">
+        <v>42047</v>
+      </c>
+      <c r="D5" s="10">
+        <v>15</v>
+      </c>
+      <c r="E5" s="29">
+        <v>457.97989999999999</v>
+      </c>
+      <c r="F5" s="29">
+        <v>6869.7</v>
+      </c>
+      <c r="G5" s="29">
+        <v>6869.7</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="N5">
+        <f>N4-D5</f>
+        <v>12.235999999999997</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="10">
+        <v>96</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="11">
+        <v>42208</v>
+      </c>
+      <c r="D6" s="15">
+        <v>10.042999999999999</v>
+      </c>
+      <c r="E6" s="29">
+        <v>591.1232</v>
+      </c>
+      <c r="F6" s="29">
+        <v>5936.65</v>
+      </c>
+      <c r="G6" s="29">
+        <v>5936.65</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="N6">
+        <f>N5+D6</f>
+        <v>22.278999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="10">
+        <v>104</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="11">
+        <v>42311</v>
+      </c>
+      <c r="D7" s="32">
+        <v>4.7E-2</v>
+      </c>
+      <c r="E7" s="29">
+        <v>507.0213</v>
+      </c>
+      <c r="F7" s="29">
+        <v>23.83</v>
+      </c>
+      <c r="G7" s="29">
+        <v>23.83</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="N7">
+        <f>N6+D7</f>
+        <v>22.325999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="10">
+        <v>41</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="11">
+        <v>42047</v>
+      </c>
+      <c r="D11" s="13">
+        <v>174.22900000000001</v>
+      </c>
+      <c r="E11" s="29">
+        <v>39.429099999999998</v>
+      </c>
+      <c r="F11" s="29">
+        <v>6869.7</v>
+      </c>
+      <c r="G11" s="29">
+        <v>6869.7</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="N11">
+        <f>D11</f>
+        <v>174.22900000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" thickBot="1">
+      <c r="A12" s="10">
+        <v>95</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11">
+        <v>42207</v>
+      </c>
+      <c r="D12" s="10">
+        <v>150</v>
+      </c>
+      <c r="E12" s="29">
+        <v>39.5777</v>
+      </c>
+      <c r="F12" s="29">
+        <v>5936.65</v>
+      </c>
+      <c r="G12" s="29">
+        <v>5936.65</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="N12" s="19">
+        <f>N11-D12</f>
+        <v>24.229000000000013</v>
+      </c>
+      <c r="O12" s="19">
+        <f>D12</f>
+        <v>150</v>
+      </c>
+      <c r="P12" s="1">
+        <f>P$5/D$11*O12</f>
+        <v>12.914038420699194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A13" s="10">
+        <v>187</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11">
+        <v>44176</v>
+      </c>
+      <c r="D13" s="10">
+        <v>24.228999999999999</v>
+      </c>
+      <c r="E13" s="29">
+        <v>42.515799999999999</v>
+      </c>
+      <c r="F13" s="29">
+        <v>1030.1199999999999</v>
+      </c>
+      <c r="G13" s="29">
+        <v>1030.1199999999999</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="29">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="N13" s="19">
+        <f>N12-D13</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="19">
+        <f>D13</f>
+        <v>24.228999999999999</v>
+      </c>
+      <c r="P13" s="30">
+        <f>P$5/D$11*O13</f>
+        <v>2.0859615793008053</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.5" thickTop="1" thickBot="1">
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.5" thickTop="1" thickBot="1">
+      <c r="P15" s="30">
+        <f>+N3-P13</f>
+        <v>22.006038420699195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" thickTop="1">
+      <c r="A16" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="10">
+        <v>37</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="11">
+        <v>41534</v>
+      </c>
+      <c r="D17" s="10">
+        <v>76.745999999999995</v>
+      </c>
+      <c r="E17" s="29">
+        <v>13.03</v>
+      </c>
+      <c r="F17" s="29">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="29">
+        <v>1000</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="10">
+        <v>38</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="11">
+        <v>41673</v>
+      </c>
+      <c r="D18" s="10">
+        <v>75</v>
+      </c>
+      <c r="E18" s="29">
+        <v>12.78</v>
+      </c>
+      <c r="F18" s="29">
+        <v>958.5</v>
+      </c>
+      <c r="G18" s="29">
+        <v>958.5</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="O18">
+        <f>D18</f>
+        <v>75</v>
+      </c>
+      <c r="P18" s="25">
+        <f>D18</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="10">
+        <v>103</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="11">
+        <v>42310</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1.746</v>
+      </c>
+      <c r="E19" s="29">
+        <v>13.648300000000001</v>
+      </c>
+      <c r="F19" s="29">
+        <v>23.83</v>
+      </c>
+      <c r="G19" s="29">
+        <v>23.83</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10">
+        <v>1</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="O19">
+        <f>D19</f>
+        <v>1.746</v>
+      </c>
+      <c r="P19" s="32">
+        <f>D19</f>
+        <v>1.746</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="P20">
+        <f>SUM(P18:P19)</f>
+        <v>76.745999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Docs/RepartimentDesglo�Compra.xlsx
+++ b/Docs/RepartimentDesglo�Compra.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="80" windowWidth="19140" windowHeight="7340" activeTab="6"/>
+    <workbookView xWindow="80" yWindow="80" windowWidth="19140" windowHeight="7340" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,13 +14,14 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Compra-Venda" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="386">
   <si>
     <t>c1</t>
   </si>
@@ -1154,6 +1155,30 @@
   </si>
   <si>
     <t>2-European Growth N Acc ?</t>
+  </si>
+  <si>
+    <t>Ocupat</t>
+  </si>
+  <si>
+    <t>Utilitzat</t>
+  </si>
+  <si>
+    <t>Disp.</t>
+  </si>
+  <si>
+    <t>Vendes de la compra</t>
+  </si>
+  <si>
+    <t>Compres de la venda</t>
+  </si>
+  <si>
+    <t>En cartera:</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>U</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1284,6 +1309,114 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1293,7 +1426,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1355,6 +1488,49 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent4" xfId="5" builtinId="42"/>
@@ -15607,4 +15783,507 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="7.08984375" customWidth="1"/>
+    <col min="4" max="4" width="2.08984375" customWidth="1"/>
+    <col min="11" max="11" width="9.1796875" customWidth="1"/>
+    <col min="12" max="12" width="10.81640625" customWidth="1"/>
+    <col min="14" max="14" width="3.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
+      </c>
+      <c r="P3" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="14">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
+      </c>
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="11">
+        <v>41172</v>
+      </c>
+      <c r="M4" s="10">
+        <v>325.52199999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="14">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="J5" s="10">
+        <v>2</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="11">
+        <v>41187</v>
+      </c>
+      <c r="M5" s="20">
+        <v>1267.6880000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="J6" s="10">
+        <v>3</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="11">
+        <v>41410</v>
+      </c>
+      <c r="M6" s="10">
+        <v>522.37400000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="14">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7">
+        <v>300</v>
+      </c>
+      <c r="J7" s="10">
+        <v>4</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="11">
+        <v>41438</v>
+      </c>
+      <c r="M7" s="20">
+        <v>1415.5820000000001</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f>M4</f>
+        <v>325.52199999999999</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2">
+        <v>40</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="19">
+        <f>M7-Q7</f>
+        <v>1090.0600000000002</v>
+      </c>
+      <c r="R8" s="19">
+        <f>M5-Q8</f>
+        <v>177.62799999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="J9" s="10">
+        <v>5</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="11">
+        <v>41492</v>
+      </c>
+      <c r="M9" s="10">
+        <v>178</v>
+      </c>
+      <c r="N9" s="10">
+        <v>2</v>
+      </c>
+      <c r="P9" s="19">
+        <f>Q8</f>
+        <v>1090.0600000000002</v>
+      </c>
+      <c r="Q9" s="19">
+        <f>R8</f>
+        <v>177.62799999999993</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="59" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="61"/>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="19">
+        <f>M9-Q9</f>
+        <v>0.37200000000007094</v>
+      </c>
+      <c r="R10" s="19">
+        <f>M6-Q10</f>
+        <v>522.00199999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="54"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="55" t="s">
+        <v>378</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>379</v>
+      </c>
+      <c r="G11" s="57" t="s">
+        <v>380</v>
+      </c>
+      <c r="I11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="33">
+        <f>A4</f>
+        <v>3</v>
+      </c>
+      <c r="B12" s="36">
+        <f>C4</f>
+        <v>50</v>
+      </c>
+      <c r="C12" s="35">
+        <f>A2</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36">
+        <v>0</v>
+      </c>
+      <c r="F12" s="36">
+        <v>50</v>
+      </c>
+      <c r="G12" s="53">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="56">
+        <f>A5</f>
+        <v>4</v>
+      </c>
+      <c r="B13" s="8">
+        <f>C5</f>
+        <v>10</v>
+      </c>
+      <c r="C13" s="41">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>50</v>
+      </c>
+      <c r="F13" s="8">
+        <v>10</v>
+      </c>
+      <c r="G13" s="45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="37">
+        <f>A7</f>
+        <v>6</v>
+      </c>
+      <c r="B14" s="7">
+        <f>C7</f>
+        <v>300</v>
+      </c>
+      <c r="C14" s="39">
+        <f>A2</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7">
+        <v>40</v>
+      </c>
+      <c r="G14" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="40"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="41">
+        <f>A3</f>
+        <v>2</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>200</v>
+      </c>
+      <c r="G15" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44">
+        <f>A6</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43">
+        <v>0</v>
+      </c>
+      <c r="F16" s="43">
+        <v>60</v>
+      </c>
+      <c r="G16" s="46">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="59" t="s">
+        <v>381</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="61"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="49" t="s">
+        <v>378</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="G19" s="58" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="50">
+        <f>A2</f>
+        <v>1</v>
+      </c>
+      <c r="B20" s="7">
+        <f>C2</f>
+        <v>100</v>
+      </c>
+      <c r="C20" s="38">
+        <f>A4</f>
+        <v>3</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>50</v>
+      </c>
+      <c r="G20" s="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="40"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="47">
+        <f>A5</f>
+        <v>4</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>10</v>
+      </c>
+      <c r="G21" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="48">
+        <f>A7</f>
+        <v>6</v>
+      </c>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43">
+        <v>0</v>
+      </c>
+      <c r="F22" s="43">
+        <v>40</v>
+      </c>
+      <c r="G22" s="46">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="52">
+        <f>A3</f>
+        <v>2</v>
+      </c>
+      <c r="B23" s="36">
+        <f>C3</f>
+        <v>200</v>
+      </c>
+      <c r="C23" s="34">
+        <v>6</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36">
+        <v>40</v>
+      </c>
+      <c r="F23" s="36">
+        <v>200</v>
+      </c>
+      <c r="G23" s="53">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="52">
+        <f>A6</f>
+        <v>5</v>
+      </c>
+      <c r="B24" s="36">
+        <f>C6</f>
+        <v>100</v>
+      </c>
+      <c r="C24" s="34">
+        <v>6</v>
+      </c>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36">
+        <v>240</v>
+      </c>
+      <c r="F24" s="36">
+        <v>60</v>
+      </c>
+      <c r="G24" s="53">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>